--- a/Doc/GameExcels/dic_seas.xlsx
+++ b/Doc/GameExcels/dic_seas.xlsx
@@ -1,383 +1,193 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Yijue\Shanhaijing_laya\Doc\GameExcels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17775" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>name_desc</t>
-  </si>
-  <si>
-    <t>lock</t>
-  </si>
-  <si>
-    <t>img</t>
-  </si>
-  <si>
-    <t>definition_info</t>
-  </si>
-  <si>
-    <t>definition_info_desc</t>
-  </si>
-  <si>
-    <t>Original_info</t>
-  </si>
-  <si>
-    <t>number</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>海经章节id</t>
-  </si>
-  <si>
-    <t>章节名字，键值</t>
-  </si>
-  <si>
-    <t>备注不读</t>
-  </si>
-  <si>
-    <t>1锁0不锁</t>
-  </si>
-  <si>
-    <t>插画，&amp;链接多图</t>
-  </si>
-  <si>
-    <t>现代释义，填键值</t>
-  </si>
-  <si>
-    <t>原著文本，不参与多语言</t>
-  </si>
-  <si>
-    <t>seas_chapter_1</t>
-  </si>
-  <si>
-    <t>章节名字六字</t>
-  </si>
-  <si>
-    <t>1101&amp;1102&amp;1103&amp;1104&amp;1105</t>
-  </si>
-  <si>
-    <t>definition_seas_info_1</t>
-  </si>
-  <si>
-    <t>第1章现代译文</t>
-  </si>
-  <si>
-    <t>填第1章原著文本</t>
-  </si>
-  <si>
-    <t>seas_chapter_2</t>
-  </si>
-  <si>
-    <t>2101&amp;2102&amp;2103&amp;2104&amp;2105</t>
-  </si>
-  <si>
-    <t>definition_seas_info_2</t>
-  </si>
-  <si>
-    <t>第2章现代译文</t>
-  </si>
-  <si>
-    <t>填第2章原著文本</t>
-  </si>
-  <si>
-    <t>seas_chapter_3</t>
-  </si>
-  <si>
-    <t>3101&amp;3102&amp;3103&amp;3104&amp;3105</t>
-  </si>
-  <si>
-    <t>definition_seas_info_3</t>
-  </si>
-  <si>
-    <t>第3章现代译文</t>
-  </si>
-  <si>
-    <t>填第3章原著文本</t>
-  </si>
-  <si>
-    <t>seas_chapter_4</t>
-  </si>
-  <si>
-    <t>4101&amp;4102&amp;4103&amp;4104&amp;4105</t>
-  </si>
-  <si>
-    <t>definition_seas_info_4</t>
-  </si>
-  <si>
-    <t>第4章现代译文</t>
-  </si>
-  <si>
-    <t>填第4章原著文本</t>
-  </si>
-  <si>
-    <t>seas_chapter_5</t>
-  </si>
-  <si>
-    <t>5101&amp;5102&amp;5103&amp;5104&amp;5105</t>
-  </si>
-  <si>
-    <t>definition_seas_info_5</t>
-  </si>
-  <si>
-    <t>第5章现代译文</t>
-  </si>
-  <si>
-    <t>填第5章原著文本</t>
-  </si>
-  <si>
-    <t>seas_chapter_6</t>
-  </si>
-  <si>
-    <t>6101&amp;6102&amp;6103&amp;6104&amp;6105</t>
-  </si>
-  <si>
-    <t>definition_seas_info_6</t>
-  </si>
-  <si>
-    <t>第6章现代译文</t>
-  </si>
-  <si>
-    <t>填第6章原著文本</t>
-  </si>
-  <si>
-    <t>seas_chapter_7</t>
-  </si>
-  <si>
-    <t>7101&amp;7102&amp;7103&amp;7104&amp;7105</t>
-  </si>
-  <si>
-    <t>definition_seas_info_7</t>
-  </si>
-  <si>
-    <t>第7章现代译文</t>
-  </si>
-  <si>
-    <t>填第7章原著文本</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="22">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="36">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -710,176 +520,177 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -933,11 +744,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1189,284 +1063,4370 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H114"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="21.125" customWidth="1"/>
-    <col min="3" max="3" width="17.625" customWidth="1"/>
-    <col min="4" max="4" width="8.875" customWidth="1"/>
-    <col min="5" max="5" width="30.875" customWidth="1"/>
-    <col min="6" max="6" width="23.875" customWidth="1"/>
-    <col min="7" max="7" width="42.875" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
+    <col width="11.5" customWidth="1" style="7" min="1" max="1"/>
+    <col width="21.125" customWidth="1" style="7" min="2" max="2"/>
+    <col width="17.625" customWidth="1" style="7" min="3" max="3"/>
+    <col width="8.875" customWidth="1" style="7" min="4" max="4"/>
+    <col width="30.875" customWidth="1" style="7" min="5" max="5"/>
+    <col width="23.875" customWidth="1" style="7" min="6" max="6"/>
+    <col width="42.875" customWidth="1" style="7" min="7" max="7"/>
+    <col width="34" customWidth="1" style="7" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name_desc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>lock</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>img</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>definition_info</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>definition_info_desc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Original_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>海经章节id</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>章节名字，键值</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>备注不读</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1锁0不锁</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>插画，&amp;链接多图</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>现代释义，填键值</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>备注不读</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>原著文本，不参与多语言</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>seas_chapter_1</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>结匈国</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>definition_seas_info_1</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>第1章现代译文</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>结匈国在其西南，其为人结匈。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>seas_chapter_2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>羽民国</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>definition_seas_info_2</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>第2章现代译文</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>羽民国在其东南，其为人长头，身生羽。一曰在比翼鸟东南，其为人长颊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>seas_chapter_3</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>讙头国（讙朱国）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>definition_seas_info_3</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>第3章现代译文</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>讙头国在其南，其为人人面有翼，鸟喙，方捕鱼。一曰在毕方东。或曰讙朱国。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>seas_chapter_4</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>厌火国</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>definition_seas_info_4</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>第4章现代译文</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>厌火国在其国南，兽身黑色，生火出其口中。一曰在讙朱东。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>seas_chapter_5</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>三苗国</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>definition_seas_info_5</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>第5章现代译文</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>三苗国在赤水东，其为人相随。一曰三毛国。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>seas_chapter_6</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>臷国（盛国）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>definition_seas_info_6</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>第6章现代译文</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>臷国在其东，其为人黄，能操弓射蛇。一曰盛国。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>seas_chapter_7</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>贯匈国（穿胸国）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>definition_seas_info_7</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>第7章现代译文</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>贯匈国在其东，其为人匈有窍。一曰在臷国东。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>seas_chapter_8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>交胫国</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8101</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>definition_seas_info_8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>第8章现代译文</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>交胫国在其东，其为人交胫。一曰在穿匈东。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>seas_chapter_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>不死民</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>definition_seas_info_9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>第9章现代译文</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>不死民在其东，其为人黑色，寿，不死。一曰在穿匈国东。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="3" t="s">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>seas_chapter_10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>岐舌国（反舌国）</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>definition_seas_info_10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>第10章现代译文</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>岐舌国在其东，其为人反舌。一曰支舌国，在不死民东。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>seas_chapter_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>三首国</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>definition_seas_info_11</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>第11章现代译文</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>三首国在其东，其为人一身三首。一曰在凿齿东。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>seas_chapter_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>周饶国（侏儒国）</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>definition_seas_info_12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>第12章现代译文</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>周饶国在其东，其为人短小，冠带。一曰焦侥国，在三首东。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>seas_chapter_13</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>长臂国</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>definition_seas_info_13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>第13章现代译文</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>长臂国在其东，捕鱼水中，两手各操一鱼。一曰在焦侥东，捕鱼海中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>14</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>seas_chapter_14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>南方祝融</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>definition_seas_info_14</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>第14章现代译文</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>南方祝融，兽身人面，乘两龙。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>15</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>seas_chapter_15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>灭蒙鸟</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>definition_seas_info_15</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>第15章现代译文</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>灭蒙鸟在结匈国北，为鸟青，赤尾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>seas_chapter_16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>夏后启（大乐之野）</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>definition_seas_info_16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>第16章现代译文</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>大乐之野，夏后启于此儛九代，乘两龙，云盖三层。左手操翳，右手操环，佩玉璜。在大运山北。一曰大遗之野。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>seas_chapter_17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>三身国</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>17101</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>definition_seas_info_17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>第17章现代译文</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>三身国在夏后启北，一首而三身。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
         <v>18</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>seas_chapter_18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>一臂国（一臂一目）</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>18101</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>definition_seas_info_18</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>第18章现代译文</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>一臂国在其北，一臂、一目、一鼻孔。有黄马虎文，一目而一手。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>19</v>
       </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>seas_chapter_19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>奇肱之国</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>19101</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>definition_seas_info_19</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>第19章现代译文</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>奇肱之国在其北，其人一臂三目，有阴有阳，乘文马。有鸟焉，两头，赤黄色，在其旁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
         <v>20</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>seas_chapter_20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>形天（刑天）</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>20101</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>definition_seas_info_20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>第20章现代译文</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>刑天与帝至此争神，帝断其首，葬之常羊之山。乃以乳为目，以脐为口，操干戚以舞。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>21</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>seas_chapter_21</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>女祭女戚</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>21101</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>definition_seas_info_21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>第21章现代译文</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>女祭、女戚在其北，居两水间，戚操鱼䱇，祭操俎。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>22</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>seas_chapter_22</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>丈夫国</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>22101</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>definition_seas_info_22</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>第22章现代译文</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>丈夫国在维鸟北，其为人衣冠带剑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="4">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>seas_chapter_23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>巫咸国</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>23101</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>definition_seas_info_23</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>第23章现代译文</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>巫咸国在女丑北，右手操青蛇，左手操赤蛇，在登葆山，群巫所从上下也。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>24</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>seas_chapter_24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>女子国（女儿国）</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>24101</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>definition_seas_info_24</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>第24章现代译文</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>女子国在巫咸北，两女子居，水周之。一曰居一门中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>25</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>seas_chapter_25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>轩辕之国</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>25101</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>definition_seas_info_25</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>第25章现代译文</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>轩辕之国在此穷山之际，其不寿者八百岁。在女子国北。人面蛇身，尾交首上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>26</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>seas_chapter_26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>穷山</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>26101</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>definition_seas_info_26</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>第26章现代译文</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>穷山在其北，不敢西射，畏轩辕之丘。在轩辕国北。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>seas_chapter_27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>乘黄（飞黄）</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>27101</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>definition_seas_info_27</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>第27章现代译文</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>白民之国在龙鱼北，白身被发。有乘黄，其状如狐，其背上有角，乘之寿二千岁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="4">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>seas_chapter_28</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>西王母（海外西经）</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>28101</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>definition_seas_info_28</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>第28章现代译文</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>西王母居玉山，是司天之厉及五残。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
         <v>29</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>seas_chapter_29</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>东方句芒</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>29101</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>definition_seas_info_29</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>第29章现代译文</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>东方句芒，鸟身人面，乘两龙。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>30</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>seas_chapter_30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>烛阴（烛龙）</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>30101</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>definition_seas_info_30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>第30章现代译文</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>钟山之神，名曰烛阴，视为昼，瞑为夜，吹为冬，呼为夏，不饮，不食，不息，息为风。身长千里。在无䏿之东。其为物，人面蛇身，赤色，居钟山下。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>31</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>seas_chapter_31</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>一目国</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>31101</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>definition_seas_info_31</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>第31章现代译文</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>一目国在其东，一目中其面而居。一曰有手足。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>32</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>seas_chapter_32</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>柔利国</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>32101</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>definition_seas_info_32</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>第32章现代译文</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>柔利国在一目东，为人一手一足，反膝，曲足居上。一云留利之国，人足反折。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="4">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>seas_chapter_33</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>共工之臣相柳</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>33101</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>definition_seas_info_33</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>第33章现代译文</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>共工之臣曰相柳氏，九首，蛇身而青。不敢北射，畏共工之台。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>seas_chapter_34</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>深目国</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>34101</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>definition_seas_info_34</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>第34章现代译文</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>深目国在其东，为人举一手。一曰在共工台东。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>35</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>seas_chapter_35</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>无肠国</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>35101</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>definition_seas_info_35</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>第35章现代译文</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>无肠之国在深目东，其为人长肘。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
         <v>36</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>seas_chapter_36</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>聂耳国</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>36101</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>definition_seas_info_36</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>第36章现代译文</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>聂耳之国在无肠国东，使两文虎，为人两手聂其耳。县居海水中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
         <v>37</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>seas_chapter_37</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>夸父（博父国）</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>37101</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>definition_seas_info_37</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>第37章现代译文</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>博父国在聂耳东，其为人大，右手操青蛇，左手操黄蛇。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="4">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>seas_chapter_38</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>拘缨国（拘瘿国）</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>38101</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>definition_seas_info_38</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>第38章现代译文</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>拘缨之国在其东，一手把缨。一曰利缨之国。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
         <v>39</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>seas_chapter_39</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>跂踵国</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>39101</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>definition_seas_info_39</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>第39章现代译文</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>跂踵国在拘缨东，其为人大，两足亦大。一曰大踵。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
         <v>40</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>seas_chapter_40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>欧丝之野</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>40101</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>definition_seas_info_40</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>第40章现代译文</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>欧丝之野在反踵东，一女子跪据树欧丝。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
         <v>41</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>seas_chapter_41</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>北方禺彊（禺强）</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>41101</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>definition_seas_info_41</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>第41章现代译文</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>北方禺彊，人面鸟身，珥两青蛇，践两青蛇。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
         <v>42</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>seas_chapter_42</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>大人国</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>42101</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>definition_seas_info_42</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>第42章现代译文</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>大人国在其北，为人大，坐而削船。一曰在䟣丘北。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="4">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>seas_chapter_43</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>君子国</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>43101</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>definition_seas_info_43</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>第43章现代译文</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>君子国在其北，衣冠带剑，食兽，使二大虎在旁，其人好让不争。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
         <v>44</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>seas_chapter_44</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>天吴（朝阳之谷）</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>44101</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>definition_seas_info_44</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>第44章现代译文</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>朝阳之谷，神曰天吴，是为水伯。在虹虹北两水间。其为兽也，八首人面，八足八尾，皆青黄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
         <v>45</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>seas_chapter_45</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>青丘国（九尾狐）</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>45101</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>definition_seas_info_45</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>第45章现代译文</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>青丘国在其北，其狐四足九尾。一曰在朝阳北。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
         <v>46</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>seas_chapter_46</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>黑齿国</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>46101</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>definition_seas_info_46</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>第46章现代译文</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>黑齿国在其北，为人黑齿，食稻啖蛇，一赤一青，在其旁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
         <v>47</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>seas_chapter_47</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>雨师妾</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>47101</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>definition_seas_info_47</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>第47章现代译文</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>雨师妾在其北，其为人黑，两手各操一蛇，左耳有青蛇，右耳有赤蛇。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="4">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>seas_chapter_48</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>玄股之国</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>48101</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>definition_seas_info_48</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>第48章现代译文</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>玄股之国在其北，其为人衣鱼食䰻，使两鸟夹之。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
         <v>49</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>seas_chapter_49</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>毛民之国</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>49101</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>definition_seas_info_49</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>第49章现代译文</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>毛民之国在其北，为人身生毛。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
         <v>50</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>seas_chapter_50</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>劳民国（教民）</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>50101</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>definition_seas_info_50</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>第50章现代译文</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>劳民国在其北，其为人黑。或曰教民。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
         <v>51</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>seas_chapter_51</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>枭阳国（狒狒）</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>51101</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>definition_seas_info_51</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>第51章现代译文</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>枭阳国在北朐之西，其为人人面长唇，黑身有毛，反踵，见人笑亦笑，左手操管。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
         <v>52</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>seas_chapter_52</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>兕</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>52101</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>definition_seas_info_52</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>第52章现代译文</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>兕在舜葬东，湘水南，其状如牛，苍黑，一角。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
         <v>53</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>seas_chapter_53</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>苍梧山（舜葬）</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>53101</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>definition_seas_info_53</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>第53章现代译文</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>苍梧之山，帝舜葬于阳，帝丹朱葬于阴。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>seas_chapter_54</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>窫窳（猰貐）</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>54101</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>definition_seas_info_54</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>第54章现代译文</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>窫窳居弱水中，在狌狌之西，其状如龍首，食人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>seas_chapter_55</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>狍鸮（饕餮）</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>55101</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>definition_seas_info_55</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>第55章现代译文</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>狍鸮其状如羊身人面，其目在腋下，虎齿人爪，其音如婴儿，食人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>seas_chapter_56</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>海内昆仑虚（帝之下都）</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>56101</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>definition_seas_info_56</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>第56章现代译文</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>海内昆仑之虚，在西北，帝之下都。昆仑之虚，方八百里，高万仞。上有木禾，长五寻，大五围。面有九井，以玉为槛。面有九门，门有开明兽守之。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>seas_chapter_57</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>开明兽</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>57101</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>definition_seas_info_57</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>第57章现代译文</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>昆仑南渊深三百仞。开明兽身大类虎而九首，皆人面，东向立昆仑上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>seas_chapter_58</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>凤凰鸾鸟</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>58101</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>definition_seas_info_58</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>第58章现代译文</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>有鸟焉，其状如蜂，大如鸳鸯，五色而文，名曰鸾鸟。又有青鸟、琅鸟、玄鸟、黄鸟，相群自歌。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>seas_chapter_59</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>不死树与珠树文玉树</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>59101</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>definition_seas_info_59</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>第59章现代译文</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>有不死树，食之乃寿。又有珠树、文玉树、玗琪树、不死树。离朱、视肉、邛邛、寻木。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>seas_chapter_60</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>弱水与流沙</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>60101</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>definition_seas_info_60</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>第60章现代译文</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>弱水、青水出西南隅，以东行，又北，又西南，过毕方鸟东。流沙出钟山，西行又南行昆仑之虚。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>seas_chapter_61</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>后稷之葬（都广之野）</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>61101</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>definition_seas_info_61</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>第61章现代译文</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>后稷之葬，山水环之。在氐国西。爰有膏菽、膏稻、膏黍、膏稷，百谷自生，冬夏播琴。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>seas_chapter_62</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>建木（众帝所自上下）</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>62101</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>definition_seas_info_62</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>第62章现代译文</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>有木，其状如牛，引之有皮，若缨黄蛇。其叶如罗，其实如栾，其木若蓲，其名曰建木。众帝所自上下。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>seas_chapter_63</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>犬戎国</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>63101</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>definition_seas_info_63</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>第63章现代译文</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>犬戎国，其为人状如人，而犬首。黄帝生苗龙，苗龙生融吾，融吾生弄明，弄明生白犬，白犬有牝牡，是为犬戎。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>seas_chapter_64</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>穷奇（北海）</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>64101</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>definition_seas_info_64</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>第64章现代译文</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>穷奇状如虎，有翼，食人从首始。所食被发。在蜪犬北。为物，状如牛，猬毛，名曰穷奇，音如獆狗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>seas_chapter_65</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>帝尧台、帝喾台、丹朱台</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>65101</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>definition_seas_info_65</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>第65章现代译文</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>帝尧台、帝喾台、帝丹朱台、帝舜台，各二台，台四方，在昆仑东北。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>seas_chapter_66</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>贰负与危（杀窫窳）</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>66101</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>definition_seas_info_66</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>第66章现代译文</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>贰负之臣曰危，危与贰负杀窫窳。帝乃梏之疏属之山，桎其右足，反缚两手与发，系之山上木。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>seas_chapter_67</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>大蟹与陵鱼</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>67101</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>definition_seas_info_67</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>第67章现代译文</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>大蟹在海中。陵鱼人面，手足，鱼身，在海中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>seas_chapter_68</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>蓬莱山</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>68101</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>definition_seas_info_68</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>第68章现代译文</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>蓬莱山在海中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>seas_chapter_69</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>大人之市</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>69101</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>definition_seas_info_69</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>第69章现代译文</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>大人之市在海中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>seas_chapter_70</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>钜燕（大燕）</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>70101</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>definition_seas_info_70</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>第70章现代译文</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>国在流沙中者埻端、玺㬇，在昆仑虚东南。一曰海内之郡，不为郡县，在流沙中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>seas_chapter_71</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>琅邪台与渤海</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>71101</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>definition_seas_info_71</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>第71章现代译文</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>琅邪台在渤海间，琅邪之东。其北有山。一曰在海间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>seas_chapter_72</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>雷泽与兖水</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>72101</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>definition_seas_info_72</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>第72章现代译文</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>雷泽中有雷神，龙身而人头，鼓其腹。在吴西。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>seas_chapter_73</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>少昊之国</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>73101</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>definition_seas_info_73</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>第73章现代译文</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>东海之外大壑，少昊之国。少昊孺帝颛顼于此，弃其琴瑟。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>seas_chapter_74</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>大言山（日月所出之一）</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>74101</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>definition_seas_info_74</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>第74章现代译文</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>大荒之中，有山名曰大言，日月所出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>seas_chapter_75</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>中容国（中容之国）</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>75101</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>definition_seas_info_75</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>第75章现代译文</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>有中容之国。帝俊生中容。中容人食兽、木实，使四鸟：豹、虎、熊、罴。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>seas_chapter_76</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>应龙（杀蚩尤与夸父）</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>76101</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>definition_seas_info_76</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>第76章现代译文</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>应龙处南极，杀蚩尤与夸父，不得复上，故下数旱。旱而为应龙之状，乃得大雨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>seas_chapter_77</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>禺䝞（东海海神）</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>77101</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>definition_seas_info_77</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>第77章现代译文</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>东海之渚中，有神，人面鸟身，珥两黄蛇，践两黄蛇，名曰禺䝞。黄帝生禺䝞，禺䝞生禺京。禺京处北海，禺䝞处东海，是惟海神。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>seas_chapter_78</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>大人国（大荒）与靖人</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>78101</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>definition_seas_info_78</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>第78章现代译文</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>有大人之国，有大人之市。有小人国，名靖人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>seas_chapter_79</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>甘山（帝俊竹林）</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>79101</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>definition_seas_info_79</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>第79章现代译文</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>有甘山者，甘水出焉，生甘渊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>seas_chapter_80</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>日月山（颛顼令重黎绝地天通）</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>80101</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>definition_seas_info_80</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>第80章现代译文</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>大荒之中，有山名曰日月山，天枢也。吴姖天门，日月所入。有神，人面无臂，两足反属于头山，名曰嘘。颛顼生老童，老童生重及黎，帝令重献上天，令黎卬下地，下地是生噎，处于西极，以行日月星辰之行次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>seas_chapter_81</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>羽民（大荒）与卵民</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>81101</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>definition_seas_info_81</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>第81章现代译文</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>有羽民之国，其民皆生毛羽。有卵民之国，其民皆生卵。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>seas_chapter_82</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>不姜山与不庭之山</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>82101</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>definition_seas_info_82</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>第82章现代译文</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>有不姜之山，黑水穷焉。又有贾山，又有言山。有不庭之山。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>seas_chapter_83</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>盈民国与不死国</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>83101</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>definition_seas_info_83</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>第83章现代译文</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>有盈民之国，于姓，黍食。又有不死之国，阿姓，甘木是食。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>seas_chapter_84</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>蜮山（蜮民）</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>84101</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>definition_seas_info_84</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>第84章现代译文</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>有蜮山者，有蜮民之国，桑姓，食黍，射蜮是食。有人方扜弓射黄蛇，名曰蜮人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>seas_chapter_85</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>宋山（枫木与丹朱）</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>85101</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>definition_seas_info_85</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>第85章现代译文</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>有宋山者，有赤蛇，名曰育蛇。有木生山上，名曰枫木。枫木，蚩尤所弃其桎梏，是为枫木。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>seas_chapter_86</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>祖状之尸与焦侥</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>86101</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>definition_seas_info_86</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>第86章现代译文</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>有祖状之尸，方齿虎尾。有焦侥之国，几姓，黍食。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>seas_chapter_87</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>寿麻国</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>87101</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>definition_seas_info_87</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>第87章现代译文</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>有寿麻之国。南岳娶州山女，名曰女虔。女虔生季格，季格生寿麻。寿麻正立无景，疾呼无响。爰有大暑，不可以往。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>seas_chapter_88</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>盖犹山与猴王</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>88101</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>definition_seas_info_88</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>第88章现代译文</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>有盖犹之山者，其上有甘柤，枝干皆赤，黄叶白华黑实。东又有甘华，枝干皆赤，黄叶。有狙，状如猿，黑臂，抵虎，名曰狙。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>seas_chapter_89</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>不周山（共工怒触）</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>89101</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>definition_seas_info_89</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>第89章现代译文</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>西北海之外，大荒之隅，有山而不合，名曰不周，有两黄兽守之。有水曰寒暑之水。共工之臣曰相柳……有禹攻共工国山。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>seas_chapter_90</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>女娲之肠（女娲化生）</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>90101</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>definition_seas_info_90</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>第90章现代译文</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>有神十人，名曰女娲之肠，化为神，处栗广之野，横道而处。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>seas_chapter_91</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>石夷（西方神）</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>91101</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>definition_seas_info_91</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>第91章现代译文</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>有人名曰石夷，来风曰韦，处西北隅，以司日月之长短。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>seas_chapter_92</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>西周之国（稷与叔均）</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>92101</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>definition_seas_info_92</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>第92章现代译文</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>有西周之国，姬姓，食谷。帝俊生后稷，稷降以百谷。稷之弟曰台玺，生叔均。叔均是代其父及稷播百谷，始作耕。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>seas_chapter_93</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>太子长琴（祝融之子）</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>93101</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>definition_seas_info_93</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>第93章现代译文</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>有榣山，其上有人，号曰太子长琴。颛顼生老童，老童生祝融，祝融生太子长琴，是处榣山，始作乐风。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>seas_chapter_94</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>常羲浴月（生月十有二）</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>94101</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>definition_seas_info_94</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>第94章现代译文</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>有女子方浴月。帝俊妻常羲，生月十有二，此始浴之。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>seas_chapter_95</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>夏后开（启）得乐</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>95101</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>definition_seas_info_95</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>第95章现代译文</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>西南海之外，赤水之南，流沙之西，有人珥两青蛇，乘两龙，名曰夏后开。开上三嫔于天，得《九辩》与《九歌》以下。此天穆之野，高二千仞，开焉始得歌《九招》。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>seas_chapter_96</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>偏句与常羊（刑天所葬）</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>96101</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>definition_seas_info_96</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>第96章现代译文</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>大荒之中，有山名曰常羊之山。有偏句、常羊之山。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>seas_chapter_97</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>附禺山（颛顼与九嫔葬）</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>97101</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>definition_seas_info_97</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>第97章现代译文</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>东北海之外，大荒之中，河水之间，附禺之山，帝颛顼与九嫔葬焉。有鸱久、文贝、离俞、鸾鸟、凤鸟……皆出卫于山。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>seas_chapter_98</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>胡不与国与叔歜国</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>98101</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>definition_seas_info_98</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>第98章现代译文</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>有胡不与之国，烈姓，黍食。有大人之国，有大青蛇，朱身，食尘。有叔歜国，颛顼之子，黍食，使四鸟：虎、豹、熊、罴。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>seas_chapter_99</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>犬戎（大荒，黄帝生苗龙系）</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>99101</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>definition_seas_info_99</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>第99章现代译文</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>有犬戎国。有神，人面兽身，名曰犬戎。黄帝生苗龙，苗龙生融吾，融吾生弄明，弄明生白犬，白犬有牝牡，是为犬戎。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>seas_chapter_100</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>九凤与强良</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>100101&amp;100102</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>definition_seas_info_100</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>第100章现代译文</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>大荒之中，有山名曰北极天柜，海水北注焉。有神，九首人面鸟身，名曰九凤。又有神，衔蛇操蛇，其状虎首人身，四蹄长肘，名曰强良。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>101</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>seas_chapter_101</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>夸父追日（大荒北）</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>101101</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>definition_seas_info_101</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>第101章现代译文</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>大荒之中，有山名曰成都载天。有人珥两黄蛇，把两黄蛇，名曰夸父。后土生信，信生夸父。夸父不量力，欲追日景，逮之于禺谷。将饮河而不足也，将走大泽，未至，死于此。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>102</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>seas_chapter_102</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>帝舜与帝丹朱之台（大荒北）</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>102101</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>definition_seas_info_102</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>第102章现代译文</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>有山名曰融父山，顺水入焉。有人名曰犬戎。有帝俊竹林，在焉，大可为舟。有赤泽水，其中生朱木。有先民之山，有槃木千里。有叔歜国。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>103</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>seas_chapter_103</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>苗民与颛顼系</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>103101</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>definition_seas_info_103</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>第103章现代译文</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>有苗民。颛顼生驩头，驩头生苗民。苗民厘姓，食肉。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>104</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>seas_chapter_104</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>钉灵之国</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>104101</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>definition_seas_info_104</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>第104章现代译文</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>有钉灵之国，其民从膝已下有毛，马蹄善走。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>105</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>seas_chapter_105</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>朝鲜与天毒</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>105101</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>definition_seas_info_105</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>第105章现代译文</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>东海之内，北海之隅，有国名曰朝鲜、天毒，其人水居，偎人爱之。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>106</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>seas_chapter_106</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>韩流（帝颛顼之父）</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>106101</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>definition_seas_info_106</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>第106章现代译文</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>流沙之东，黑水之西，有朝云之国、司彘之国。黄帝妻雷祖，生昌意。昌意降处若水，生韩流。韩流擢首、谨耳、人面、豕喙、麟身、渠股、豚止，取淖子曰阿女，生帝颛顼。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>107</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>seas_chapter_107</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>巴蛇吞象</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>107101</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>definition_seas_info_107</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>第107章现代译文</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>有巴遂之山。又有朱卷之国。有黑蛇，青首，食象。巴蛇食象，三岁而出其骨，君子服之，无心腹之疾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>108</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>seas_chapter_108</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>后稷与台玺（农耕之始）</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>108101</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>definition_seas_info_108</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>第108章现代译文</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>西南黑水之间，有都广之野，后稷葬焉。其城方三百里，盖天地之中，素女所出也。大暤爰过，黄帝所为。后稷是播百谷。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>109</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>seas_chapter_109</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>鲧禹治水（海内经核心）</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>109101&amp;109102</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>definition_seas_info_109</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>第109章现代译文</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>洪水滔天。鲧窃帝之息壤以堙洪水，不待帝命。帝令祝融杀鲧于羽郊。鲧复生禹。帝乃命禹卒布土以定九州。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>110</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>seas_chapter_110</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>鸱久与猩猩</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>definition_seas_info_110</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>第110章现代译文</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>有禺中之国。有列襄之国。有灵山，有赤蛇在木上，名曰蠕蛇，木则枫木。有猩猩之兽，人面，长唇，能言。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>111</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>seas_chapter_111</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>钉灵与匈奴</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>111101</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>definition_seas_info_111</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>第111章现代译文</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>北海之内，有山，名曰幽都之山，黑水出焉。其上有玄鸟、玄蛇、玄虎、玄狐蓬尾。有大玄之山。有玄丘之民。有大幽之国。有赤胫之民。</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>